--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="13060"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data Report" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
+  <si>
+    <t>日期</t>
+  </si>
   <si>
     <t>计划</t>
   </si>
@@ -54,6 +57,9 @@
   </si>
   <si>
     <t>完成注册</t>
+  </si>
+  <si>
+    <t>date</t>
   </si>
   <si>
     <t>Campaign</t>
@@ -136,7 +142,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -148,6 +154,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -641,152 +653,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -805,23 +817,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1371,857 +1389,946 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="2" width="23.4333333333333" style="3" customWidth="1"/>
-    <col min="3" max="4" width="23.4333333333333" style="4" customWidth="1"/>
-    <col min="5" max="6" width="23.4333333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="28.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22.875" style="3" customWidth="1"/>
-    <col min="10" max="16362" width="12.7166666666667" style="3"/>
-    <col min="16363" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="27.4038461538462" style="3" customWidth="1"/>
+    <col min="2" max="2" width="62.2307692307692" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.4326923076923" style="3" customWidth="1"/>
+    <col min="4" max="5" width="23.4326923076923" style="4" customWidth="1"/>
+    <col min="6" max="7" width="23.4326923076923" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.0769230769231" style="3" customWidth="1"/>
+    <col min="9" max="9" width="28.625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="3" customWidth="1"/>
+    <col min="11" max="16363" width="12.7211538461538" style="3"/>
+    <col min="16364" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:10">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="F2" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="G2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:9">
-      <c r="A3" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:10">
+      <c r="A3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="F3" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="G3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:9">
-      <c r="A4" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>28</v>
       </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:10">
+      <c r="A4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="13">
+      <c r="D4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15">
         <v>105.42</v>
       </c>
-      <c r="C5" s="14">
+      <c r="D5" s="16">
         <v>22852</v>
       </c>
-      <c r="D5" s="14">
+      <c r="E5" s="16">
         <v>349</v>
       </c>
-      <c r="E5" s="13">
+      <c r="F5" s="15">
         <v>87</v>
       </c>
-      <c r="F5" s="13">
+      <c r="G5" s="15">
         <v>12</v>
       </c>
-      <c r="G5" s="15">
+      <c r="H5" s="17">
         <v>1.21</v>
       </c>
-      <c r="H5" s="13">
+      <c r="I5" s="15">
         <v>8.79</v>
       </c>
-      <c r="I5" s="16">
+      <c r="J5" s="18">
         <v>1.53</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="13">
+    <row r="6" spans="1:10">
+      <c r="A6" s="13">
+        <v>46148</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="15">
         <v>96.23</v>
       </c>
-      <c r="C6" s="14">
+      <c r="D6" s="16">
         <v>1200</v>
       </c>
-      <c r="D6" s="14">
+      <c r="E6" s="16">
         <v>128</v>
       </c>
-      <c r="E6" s="13">
+      <c r="F6" s="15">
         <v>27</v>
       </c>
-      <c r="F6" s="13">
+      <c r="G6" s="15">
         <v>10</v>
       </c>
-      <c r="G6" s="13">
+      <c r="H6" s="15">
         <v>4</v>
       </c>
-      <c r="H6" s="13">
+      <c r="I6" s="15">
         <v>4.7</v>
       </c>
-      <c r="I6" s="16">
+      <c r="J6" s="18">
         <v>2.71</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="13">
+    <row r="7" spans="1:10">
+      <c r="A7" s="13">
+        <v>46146</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="15">
         <v>389.32</v>
       </c>
-      <c r="C7" s="14">
+      <c r="D7" s="16">
         <v>20001000</v>
       </c>
-      <c r="D7" s="14">
+      <c r="E7" s="16">
         <v>517</v>
       </c>
-      <c r="E7" s="13">
+      <c r="F7" s="15">
         <v>86</v>
       </c>
-      <c r="F7" s="13">
+      <c r="G7" s="15">
         <v>46</v>
       </c>
-      <c r="G7" s="13">
+      <c r="H7" s="15">
         <v>23</v>
       </c>
-      <c r="H7" s="13">
+      <c r="I7" s="15">
         <v>5.31</v>
       </c>
-      <c r="I7" s="16">
+      <c r="J7" s="18">
         <v>2.67</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="13">
+    <row r="8" spans="1:10">
+      <c r="A8" s="13">
+        <v>46146</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="15">
         <v>2234201.66</v>
       </c>
-      <c r="C8" s="14">
+      <c r="D8" s="16">
         <v>300001200</v>
       </c>
-      <c r="D8" s="14">
+      <c r="E8" s="16">
         <v>37633241</v>
       </c>
-      <c r="E8" s="13">
+      <c r="F8" s="15">
         <v>352233358</v>
       </c>
-      <c r="F8" s="13">
+      <c r="G8" s="15">
         <v>11112216</v>
       </c>
-      <c r="G8" s="13">
+      <c r="H8" s="15">
         <v>3256633329</v>
       </c>
-      <c r="H8" s="13">
+      <c r="I8" s="15">
         <v>4446233226.18</v>
       </c>
-      <c r="I8" s="16">
+      <c r="J8" s="18">
         <v>2.63</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="13">
+    <row r="9" spans="1:10">
+      <c r="A9" s="13">
+        <v>46148</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="15">
         <v>2123360.58</v>
       </c>
-      <c r="C9" s="14">
+      <c r="D9" s="16">
         <v>1000</v>
       </c>
-      <c r="D9" s="14">
+      <c r="E9" s="16">
         <v>987445483</v>
       </c>
-      <c r="E9" s="13">
+      <c r="F9" s="15">
         <v>4446462107</v>
       </c>
-      <c r="F9" s="13">
+      <c r="G9" s="15">
         <v>332355350</v>
       </c>
-      <c r="G9" s="13">
+      <c r="H9" s="15">
         <v>17</v>
       </c>
-      <c r="H9" s="13">
+      <c r="I9" s="15">
         <v>4.7</v>
       </c>
-      <c r="I9" s="16">
+      <c r="J9" s="18">
         <v>2.59</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="13">
+    <row r="10" spans="1:10">
+      <c r="A10" s="13">
+        <v>46143</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="15">
         <v>170.59</v>
       </c>
-      <c r="C10" s="14">
+      <c r="D10" s="16">
         <v>1200</v>
       </c>
-      <c r="D10" s="14">
+      <c r="E10" s="16">
         <v>188</v>
       </c>
-      <c r="E10" s="13">
+      <c r="F10" s="15">
         <v>45</v>
       </c>
-      <c r="F10" s="13">
+      <c r="G10" s="15">
         <v>9</v>
       </c>
-      <c r="G10" s="13">
+      <c r="H10" s="15">
         <v>5</v>
       </c>
-      <c r="H10" s="13">
+      <c r="I10" s="15">
         <v>5.31</v>
       </c>
-      <c r="I10" s="16">
+      <c r="J10" s="18">
         <v>2.55</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="13">
+    <row r="11" spans="1:10">
+      <c r="A11" s="13">
+        <v>46143</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="15">
         <v>427.82</v>
       </c>
-      <c r="C11" s="14">
+      <c r="D11" s="16">
         <v>1000</v>
       </c>
-      <c r="D11" s="14">
+      <c r="E11" s="16">
         <v>517</v>
       </c>
-      <c r="E11" s="13">
+      <c r="F11" s="15">
         <v>102</v>
       </c>
-      <c r="F11" s="13">
+      <c r="G11" s="15">
         <v>59</v>
       </c>
-      <c r="G11" s="13">
+      <c r="H11" s="15">
         <v>27</v>
       </c>
-      <c r="H11" s="13">
+      <c r="I11" s="15">
         <v>6.18</v>
       </c>
-      <c r="I11" s="16">
+      <c r="J11" s="18">
         <v>2.51</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="13">
+    <row r="12" spans="1:10">
+      <c r="A12" s="13">
+        <v>46144</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="15">
         <v>212.92</v>
       </c>
-      <c r="C12" s="14">
+      <c r="D12" s="16">
         <v>1200</v>
       </c>
-      <c r="D12" s="14">
+      <c r="E12" s="16">
         <v>210</v>
       </c>
-      <c r="E12" s="13">
+      <c r="F12" s="15">
         <v>39</v>
       </c>
-      <c r="F12" s="13">
+      <c r="G12" s="15">
         <v>12</v>
       </c>
-      <c r="G12" s="13">
+      <c r="H12" s="15">
         <v>7</v>
       </c>
-      <c r="H12" s="13">
+      <c r="I12" s="15">
         <v>6.18</v>
       </c>
-      <c r="I12" s="16">
+      <c r="J12" s="18">
         <v>2.47</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="13">
+    <row r="13" spans="1:10">
+      <c r="A13" s="13">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="15">
         <v>446.02</v>
       </c>
-      <c r="C13" s="14">
+      <c r="D13" s="16">
         <v>1000</v>
       </c>
-      <c r="D13" s="14">
+      <c r="E13" s="16">
         <v>500</v>
       </c>
-      <c r="E13" s="13">
+      <c r="F13" s="15">
         <v>123</v>
       </c>
-      <c r="F13" s="13">
+      <c r="G13" s="15">
         <v>46</v>
       </c>
-      <c r="G13" s="13">
+      <c r="H13" s="15">
         <v>14</v>
       </c>
-      <c r="H13" s="13">
+      <c r="I13" s="15">
         <v>4.7</v>
       </c>
-      <c r="I13" s="16">
+      <c r="J13" s="18">
         <v>2.43</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="13">
+    <row r="14" spans="1:10">
+      <c r="A14" s="13">
+        <v>46148</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="15">
         <v>337.91</v>
       </c>
-      <c r="C14" s="14">
+      <c r="D14" s="16">
         <v>1200</v>
       </c>
-      <c r="D14" s="14">
+      <c r="E14" s="16">
         <v>322</v>
       </c>
-      <c r="E14" s="13">
+      <c r="F14" s="15">
         <v>56</v>
       </c>
-      <c r="F14" s="13">
+      <c r="G14" s="15">
         <v>9</v>
       </c>
-      <c r="G14" s="13">
+      <c r="H14" s="15">
         <v>7</v>
       </c>
-      <c r="H14" s="13">
+      <c r="I14" s="15">
         <v>5.31</v>
       </c>
-      <c r="I14" s="16">
+      <c r="J14" s="18">
         <v>2.39</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="13">
+    <row r="15" spans="1:10">
+      <c r="A15" s="13">
+        <v>46144</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="15">
         <v>427.82</v>
       </c>
-      <c r="C15" s="14">
+      <c r="D15" s="16">
         <v>1000</v>
       </c>
-      <c r="D15" s="14">
+      <c r="E15" s="16">
         <v>517</v>
       </c>
-      <c r="E15" s="13">
+      <c r="F15" s="15">
         <v>102</v>
       </c>
-      <c r="F15" s="13">
+      <c r="G15" s="15">
         <v>59</v>
       </c>
-      <c r="G15" s="13">
+      <c r="H15" s="15">
         <v>27</v>
       </c>
-      <c r="H15" s="13">
+      <c r="I15" s="15">
         <v>6.18</v>
       </c>
-      <c r="I15" s="16">
+      <c r="J15" s="18">
         <v>2.51</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="13">
+    <row r="16" spans="1:10">
+      <c r="A16" s="13">
+        <v>46146</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="15">
         <v>212.92</v>
       </c>
-      <c r="C16" s="14">
+      <c r="D16" s="16">
         <v>1200</v>
       </c>
-      <c r="D16" s="14">
+      <c r="E16" s="16">
         <v>210</v>
       </c>
-      <c r="E16" s="13">
+      <c r="F16" s="15">
         <v>39</v>
       </c>
-      <c r="F16" s="13">
+      <c r="G16" s="15">
         <v>12</v>
       </c>
-      <c r="G16" s="13">
+      <c r="H16" s="15">
         <v>7</v>
       </c>
-      <c r="H16" s="13">
+      <c r="I16" s="15">
         <v>6.18</v>
       </c>
-      <c r="I16" s="16">
+      <c r="J16" s="18">
         <v>2.47</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="13">
+    <row r="17" spans="1:10">
+      <c r="A17" s="13">
+        <v>46147</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="15">
         <v>446.02</v>
       </c>
-      <c r="C17" s="14">
+      <c r="D17" s="16">
         <v>1000</v>
       </c>
-      <c r="D17" s="14">
+      <c r="E17" s="16">
         <v>500</v>
       </c>
-      <c r="E17" s="13">
+      <c r="F17" s="15">
         <v>123</v>
       </c>
-      <c r="F17" s="13">
+      <c r="G17" s="15">
         <v>46</v>
       </c>
-      <c r="G17" s="13">
+      <c r="H17" s="15">
         <v>14</v>
       </c>
-      <c r="H17" s="13">
+      <c r="I17" s="15">
         <v>4.7</v>
       </c>
-      <c r="I17" s="16">
+      <c r="J17" s="18">
         <v>2.43</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="13">
+    <row r="18" spans="1:10">
+      <c r="A18" s="13">
+        <v>46144</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="15">
         <v>337.91</v>
       </c>
-      <c r="C18" s="14">
+      <c r="D18" s="16">
         <v>1200</v>
       </c>
-      <c r="D18" s="14">
+      <c r="E18" s="16">
         <v>322</v>
       </c>
-      <c r="E18" s="13">
+      <c r="F18" s="15">
         <v>56</v>
       </c>
-      <c r="F18" s="13">
+      <c r="G18" s="15">
         <v>9</v>
       </c>
-      <c r="G18" s="13">
+      <c r="H18" s="15">
         <v>7</v>
       </c>
-      <c r="H18" s="13">
+      <c r="I18" s="15">
         <v>5.31</v>
       </c>
-      <c r="I18" s="16">
+      <c r="J18" s="18">
         <v>2.39</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="13">
+    <row r="19" spans="1:10">
+      <c r="A19" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="15">
         <v>337.91</v>
       </c>
-      <c r="C19" s="14">
+      <c r="D19" s="16">
         <v>1200</v>
       </c>
-      <c r="D19" s="14">
+      <c r="E19" s="16">
         <v>322</v>
       </c>
-      <c r="E19" s="13">
+      <c r="F19" s="15">
         <v>56</v>
       </c>
-      <c r="F19" s="13">
+      <c r="G19" s="15">
         <v>9</v>
       </c>
-      <c r="G19" s="13">
+      <c r="H19" s="15">
         <v>7</v>
       </c>
-      <c r="H19" s="13">
+      <c r="I19" s="15">
         <v>5.31</v>
       </c>
-      <c r="I19" s="16">
+      <c r="J19" s="18">
         <v>2.39</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="13">
+    <row r="20" spans="1:10">
+      <c r="A20" s="13">
+        <v>46132</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="15">
         <v>427.82</v>
       </c>
-      <c r="C20" s="14">
+      <c r="D20" s="16">
         <v>1000</v>
       </c>
-      <c r="D20" s="14">
+      <c r="E20" s="16">
         <v>517</v>
       </c>
-      <c r="E20" s="13">
+      <c r="F20" s="15">
         <v>102</v>
       </c>
-      <c r="F20" s="13">
+      <c r="G20" s="15">
         <v>59</v>
       </c>
-      <c r="G20" s="13">
+      <c r="H20" s="15">
         <v>27</v>
       </c>
-      <c r="H20" s="13">
+      <c r="I20" s="15">
         <v>6.18</v>
       </c>
-      <c r="I20" s="16">
+      <c r="J20" s="18">
         <v>2.51</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="13">
+    <row r="21" spans="1:10">
+      <c r="A21" s="13">
+        <v>46145</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="15">
         <v>212.92</v>
       </c>
-      <c r="C21" s="14">
+      <c r="D21" s="16">
         <v>1200</v>
       </c>
-      <c r="D21" s="14">
+      <c r="E21" s="16">
         <v>210</v>
       </c>
-      <c r="E21" s="13">
+      <c r="F21" s="15">
         <v>39</v>
       </c>
-      <c r="F21" s="13">
+      <c r="G21" s="15">
         <v>12</v>
       </c>
-      <c r="G21" s="13">
+      <c r="H21" s="15">
         <v>7</v>
       </c>
-      <c r="H21" s="13">
+      <c r="I21" s="15">
         <v>6.18</v>
       </c>
-      <c r="I21" s="16">
+      <c r="J21" s="18">
         <v>2.47</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="13">
+    <row r="22" spans="1:10">
+      <c r="A22" s="13">
+        <v>46148</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="15">
         <v>446.02</v>
       </c>
-      <c r="C22" s="14">
+      <c r="D22" s="16">
         <v>1000</v>
       </c>
-      <c r="D22" s="14">
+      <c r="E22" s="16">
         <v>500</v>
       </c>
-      <c r="E22" s="13">
+      <c r="F22" s="15">
         <v>123</v>
       </c>
-      <c r="F22" s="13">
+      <c r="G22" s="15">
         <v>46</v>
       </c>
-      <c r="G22" s="13">
+      <c r="H22" s="15">
         <v>14</v>
       </c>
-      <c r="H22" s="13">
+      <c r="I22" s="15">
         <v>4.7</v>
       </c>
-      <c r="I22" s="16">
+      <c r="J22" s="18">
         <v>2.43</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="13">
+    <row r="23" spans="1:10">
+      <c r="A23" s="13">
+        <v>46137</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="15">
         <v>337.91</v>
       </c>
-      <c r="C23" s="14">
+      <c r="D23" s="16">
         <v>1200</v>
       </c>
-      <c r="D23" s="14">
+      <c r="E23" s="16">
         <v>322</v>
       </c>
-      <c r="E23" s="13">
+      <c r="F23" s="15">
         <v>56</v>
       </c>
-      <c r="F23" s="13">
+      <c r="G23" s="15">
         <v>9</v>
       </c>
-      <c r="G23" s="13">
+      <c r="H23" s="15">
         <v>7</v>
       </c>
-      <c r="H23" s="13">
+      <c r="I23" s="15">
         <v>5.31</v>
       </c>
-      <c r="I23" s="16">
+      <c r="J23" s="18">
         <v>2.39</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="13">
+    <row r="24" spans="1:10">
+      <c r="A24" s="13">
+        <v>46140</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="15">
         <v>337.91</v>
       </c>
-      <c r="C24" s="14">
+      <c r="D24" s="16">
         <v>1200</v>
       </c>
-      <c r="D24" s="14">
+      <c r="E24" s="16">
         <v>322</v>
       </c>
-      <c r="E24" s="13">
+      <c r="F24" s="15">
         <v>56</v>
       </c>
-      <c r="F24" s="13">
+      <c r="G24" s="15">
         <v>9</v>
       </c>
-      <c r="G24" s="13">
+      <c r="H24" s="15">
         <v>7</v>
       </c>
-      <c r="H24" s="13">
+      <c r="I24" s="15">
         <v>5.31</v>
       </c>
-      <c r="I24" s="16">
+      <c r="J24" s="18">
         <v>2.39</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="13">
+    <row r="25" spans="1:10">
+      <c r="A25" s="13">
+        <v>46140</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="15">
         <v>337.91</v>
       </c>
-      <c r="C25" s="14">
+      <c r="D25" s="16">
         <v>1200</v>
       </c>
-      <c r="D25" s="14">
+      <c r="E25" s="16">
         <v>322</v>
       </c>
-      <c r="E25" s="13">
+      <c r="F25" s="15">
         <v>56</v>
       </c>
-      <c r="F25" s="13">
+      <c r="G25" s="15">
         <v>9</v>
       </c>
-      <c r="G25" s="13">
+      <c r="H25" s="15">
         <v>7</v>
       </c>
-      <c r="H25" s="13">
+      <c r="I25" s="15">
         <v>5.31</v>
       </c>
-      <c r="I25" s="16">
+      <c r="J25" s="18">
         <v>2.39</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="13">
+    <row r="26" spans="1:10">
+      <c r="A26" s="13">
+        <v>46136</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="15">
         <v>427.82</v>
       </c>
-      <c r="C26" s="14">
+      <c r="D26" s="16">
         <v>1000</v>
       </c>
-      <c r="D26" s="14">
+      <c r="E26" s="16">
         <v>517</v>
       </c>
-      <c r="E26" s="13">
+      <c r="F26" s="15">
         <v>102</v>
       </c>
-      <c r="F26" s="13">
+      <c r="G26" s="15">
         <v>59</v>
       </c>
-      <c r="G26" s="13">
+      <c r="H26" s="15">
         <v>27</v>
       </c>
-      <c r="H26" s="13">
+      <c r="I26" s="15">
         <v>6.18</v>
       </c>
-      <c r="I26" s="16">
+      <c r="J26" s="18">
         <v>2.51</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="13">
+    <row r="27" spans="1:10">
+      <c r="A27" s="13">
+        <v>46141</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="15">
         <v>212.92</v>
       </c>
-      <c r="C27" s="14">
+      <c r="D27" s="16">
         <v>1200</v>
       </c>
-      <c r="D27" s="14">
+      <c r="E27" s="16">
         <v>210</v>
       </c>
-      <c r="E27" s="13">
+      <c r="F27" s="15">
         <v>39</v>
       </c>
-      <c r="F27" s="13">
+      <c r="G27" s="15">
         <v>12</v>
       </c>
-      <c r="G27" s="13">
+      <c r="H27" s="15">
         <v>7</v>
       </c>
-      <c r="H27" s="13">
+      <c r="I27" s="15">
         <v>6.18</v>
       </c>
-      <c r="I27" s="16">
+      <c r="J27" s="18">
         <v>2.47</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="13">
+    <row r="28" spans="1:10">
+      <c r="A28" s="13">
+        <v>46138</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="15">
         <v>446.02</v>
       </c>
-      <c r="C28" s="14">
+      <c r="D28" s="16">
         <v>1000</v>
       </c>
-      <c r="D28" s="14">
+      <c r="E28" s="16">
         <v>500</v>
       </c>
-      <c r="E28" s="13">
+      <c r="F28" s="15">
         <v>123</v>
       </c>
-      <c r="F28" s="13">
+      <c r="G28" s="15">
         <v>46</v>
       </c>
-      <c r="G28" s="13">
+      <c r="H28" s="15">
         <v>14</v>
       </c>
-      <c r="H28" s="13">
+      <c r="I28" s="15">
         <v>4.7</v>
       </c>
-      <c r="I28" s="16">
+      <c r="J28" s="18">
         <v>2.43</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="13">
+    <row r="29" spans="1:10">
+      <c r="A29" s="13">
+        <v>46136</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="15">
         <v>337.91</v>
       </c>
-      <c r="C29" s="14">
+      <c r="D29" s="16">
         <v>1200</v>
       </c>
-      <c r="D29" s="14">
+      <c r="E29" s="16">
         <v>322</v>
       </c>
-      <c r="E29" s="13">
+      <c r="F29" s="15">
         <v>56</v>
       </c>
-      <c r="F29" s="13">
+      <c r="G29" s="15">
         <v>9</v>
       </c>
-      <c r="G29" s="13">
+      <c r="H29" s="15">
         <v>7</v>
       </c>
-      <c r="H29" s="13">
+      <c r="I29" s="15">
         <v>5.31</v>
       </c>
-      <c r="I29" s="16">
+      <c r="J29" s="18">
         <v>2.39</v>
       </c>
     </row>
